--- a/www/download/COUNTRY.BGR.zdW16.xlsx
+++ b/www/download/COUNTRY.BGR.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2.11817416149315</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2.18371429331226</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.07005100976294</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.72934797023921</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1.57324056149074</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.57150684664364</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.55771981608065</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1.4268095583422</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.33056068986913</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.4032544504951</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.47467205352132</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1.4049800946234</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1.52113657702085</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1.47312742642581</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47144455421764</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.319</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3.312</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.403</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3.485</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.565</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.703</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>3.824</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.916</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3.681</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3.585</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3.474</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3.6</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.397</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.361</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.364</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.444</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.509</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.718</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.831</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.902</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.847</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.696</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.642</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.576</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.556</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.685</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5668.832</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5712.087</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5724.447</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>5810.215</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>5951.245</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5982.292</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6194.355</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6404.473</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6723.273</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6404.128</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6105.093</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>5941.915</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>5759.768</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>5754.132</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>5962.96</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4052.673</t>
+          <t>6056075406.78583</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4053.491</t>
+          <t>6014794219.04564</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4045.796</t>
+          <t>5999681047.73044</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4139.088</t>
+          <t>5989425316.20696</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4269.04</t>
+          <t>6206350464.43204</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4358.348</t>
+          <t>6071792843.75418</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4547.328</t>
+          <t>6428004439.96085</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4737.114</t>
+          <t>6642742072.20247</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5004.953</t>
+          <t>6919063216.48206</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4733.784</t>
+          <t>6377023120.82877</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4478.89</t>
+          <t>5669959521.62501</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>4385.134</t>
+          <t>5720431417.75368</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4277.545</t>
+          <t>5478779709.00567</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4244.452</t>
+          <t>5507669312.54567</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4451.226</t>
+          <t>5898154580.46831</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1190076721.97401</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1172907064.40665</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1147082054.43752</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1150180613.17112</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1130950898.55741</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1096342509.27454</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1152012341.19541</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1104585756.99921</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1132559181.30057</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1198168015.51569</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1066615579.87233</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1003780975.87749</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1019815532.32808</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1054865179.56816</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1230186217.99206</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10317257.3260675</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9194190.74198995</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7846138.40839663</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6108148.52893448</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4969279.62304962</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4225145.25210784</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3803557.65900152</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3081719.9661739</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2687207.78236378</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2778981.49312691</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2669838.2313646</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2292395.99569229</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2360930.65711827</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2332507.30822475</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2384759.63629006</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>34014.7804219299</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>33104.4673573156</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>33338.5472286799</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>36130.4401200167</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>40121.786316609</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>43249.9444007521</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>47409.2572961262</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>54415.3996967179</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>62397.1319974398</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>52450.6445279226</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>53850.8325364152</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>55716.5286112393</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>52490.354614151</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>51918.069634084</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>54315.5647842911</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>54936.7178041274</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>53763.3023890589</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54022.6873301387</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>58713.9867794457</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>67047.4611363596</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>70846.8036169951</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>79256.7138976847</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>91877.7566753506</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>104375.951871024</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>87915.9625207093</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>86362.2298400822</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>92901.0633363677</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>86913.6648468647</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>86865.3474258383</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>93348.7167444494</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.40538801000808</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.45593536181026</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.52703277359167</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.59864177208506</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.77473505299425</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.97535255919608</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.94729104662314</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.28858870394017</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.41915361478291</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.95085158233221</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3.19916048904528</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.36861636689874</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.19443013408028</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3.02369144627335</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.61833512268199</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.11817416149315</t>
+          <t>496.504550431183</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18371429331226</t>
+          <t>496.687246197966</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.07005100976294</t>
+          <t>485.184142946732</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.72934797023921</t>
+          <t>470.587042137979</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.57324056149074</t>
+          <t>450.827708793877</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.57150684664364</t>
+          <t>423.340763657565</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.55771981608065</t>
+          <t>423.840921989606</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.4268095583422</t>
+          <t>390.177873739555</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.33056068986913</t>
+          <t>390.312882340367</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.4032544504951</t>
+          <t>420.876486039148</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.47467205352132</t>
+          <t>395.639196816063</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1.4049800946234</t>
+          <t>379.883351831139</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.52113657702085</t>
+          <t>395.818904286902</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.47312742642581</t>
+          <t>412.727392782083</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.47144455421764</t>
+          <t>458.159675386048</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-182416717.843657</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-215929528.893985</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-290345948.845147</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-354323737.155301</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-483960634.523512</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-592634198.731241</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-515245703.840817</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-579066553.127701</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-826318799.117936</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-501852710.222315</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-605804944.170833</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-450264196.929473</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-448483625.956126</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-508663740.84829</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-384105347.152033</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-129714317.791017</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-161783675.227839</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-239554035.168843</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-311908338.715959</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-459173904.266684</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-562008377.250351</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-478026089.241296</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-603321181.824638</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-862494385.081203</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-592821239.643922</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-724287974.861993</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-608313232.83277</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-575087720.311486</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-681114269.071392</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-659096884.622455</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-52702400.0526403</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>-54145853.6661461</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>-50791913.6763043</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-42415398.4393421</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>-24786730.2568276</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-30625821.4808902</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>-37219614.5995215</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>24254628.6969372</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>36175585.9632669</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>90968529.4216076</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>118483030.69116</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>158049035.903297</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>126604094.35536</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>172450528.223102</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>274991537.470423</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1690.7906429528</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1716.51901789571</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1711.26037340011</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1693.47418723968</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1701.75515524534</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1682.92878821812</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1673.02347656207</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1673.31242184685</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>1724.85258489077</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1662.82053083419</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1661.35248318762</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1659.56462832187</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1660.23473977962</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1660.68767997997</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1657.77524524592</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1707.81398246854</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1725.96149813342</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1728.31229959888</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1707.54094937262</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1707.68417225333</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1678.28345482844</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1672.98338274326</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1674.97633204543</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1717.03474126946</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1659.31114654009</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1658.72675815109</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1657.21152783798</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1657.94524011646</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1658.21789083251</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1656.22140916927</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1461.66932502169</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1580.5847189433</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2055.41675045683</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>3537.7704511314</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6624.88789856157</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>8482.00279189242</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>11684.7314361871</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>18529.773356474</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>23576.401380539</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>17466.3632214365</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>21902.3382525843</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>30158.53504069</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>28630.5117193318</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>31474.4225085672</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>31698.3004326911</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>364310300.640671</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>367960778.737485</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>467663875.831348</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>590666875.958418</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>865978341.382522</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>934386935.801225</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1068134542.07137</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1342074939.61343</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1616870165.29821</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1269008443.80692</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1486731204.42518</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1778140865.61461</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1636059891.70395</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1908515948.22475</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1843378452.38584</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5031.51744352607</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5726.12621724244</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6255.66485733858</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8633.08099550038</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>12534.2143094823</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>15711.5014457186</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>20302.6995670901</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>28373.9197099342</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>35471.2115933892</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>23662.444476495</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>25825.9290749601</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>31877.5121934913</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>32063.7862504548</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>34293.6931597343</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>34545.7146191857</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5668.832</t>
+          <t>670087768.734797</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5712.087</t>
+          <t>742069797.775492</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5724.447</t>
+          <t>778913320.429801</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5810.215</t>
+          <t>924259827.180048</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5951.245</t>
+          <t>1109005721.80372</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5982.292</t>
+          <t>1148414183.94406</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6194.355</t>
+          <t>1425577389.58573</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6404.473</t>
+          <t>1617789772.88176</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6723.273</t>
+          <t>1692282662.27948</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6404.128</t>
+          <t>1294762653.73968</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6105.093</t>
+          <t>1178756245.69511</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>5941.915</t>
+          <t>1451403698.38189</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5759.768</t>
+          <t>1435937599.86961</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>5754.132</t>
+          <t>1605830251.78792</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5962.96</t>
+          <t>1665309345.8316</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4052.673</t>
+          <t>-3569.84811850438</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4053.491</t>
+          <t>-4145.54149829914</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4045.796</t>
+          <t>-4200.24810688175</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4139.088</t>
+          <t>-5095.31054436898</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4269.04</t>
+          <t>-5909.32641092069</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4358.348</t>
+          <t>-7229.49865382618</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4547.328</t>
+          <t>-8617.96813090296</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4737.114</t>
+          <t>-9844.14635346016</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5004.953</t>
+          <t>-11894.8102128502</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4733.784</t>
+          <t>-6196.08125505849</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>4478.89</t>
+          <t>-3923.59082237582</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4385.134</t>
+          <t>-1718.97715280127</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4277.545</t>
+          <t>-3433.27453112309</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>4244.452</t>
+          <t>-2819.27065116711</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4451.226</t>
+          <t>-2847.41418649455</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6876.819</t>
+          <t>-305777468.094126</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6808.014</t>
+          <t>-374109019.038008</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6776.129</t>
+          <t>-311249444.598452</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6769.24</t>
+          <t>-333592951.22163</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6929.893</t>
+          <t>-243027380.421195</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6833.004</t>
+          <t>-214027248.142833</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7253.318</t>
+          <t>-357442847.51436</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7444.939</t>
+          <t>-275714833.268333</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7769.894</t>
+          <t>-75412496.9812747</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7307.742</t>
+          <t>-25754209.9327586</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6454.612</t>
+          <t>307974958.730063</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>6527.76</t>
+          <t>326737167.232717</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6285.33</t>
+          <t>200122291.834335</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6324.419</t>
+          <t>302685696.436833</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>5898.155</t>
+          <t>178069106.554234</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>6157.91828</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>6604.03155588613</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>7610.67103275058</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>9405.3620535915</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>10968.8933865388</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>12377.5509</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>13945.5682984223</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>17902.1309389384</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>21739.368012287</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>20831.338</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>19033.463699371</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>22583.8003997799</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>21116.8524123456</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>21068.809580309</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>21998.8213337888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3749.698</t>
+          <t>0.116661840222705</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3703.578</t>
+          <t>0.118880286711373</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3702.531</t>
+          <t>0.136157831755586</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3685.673</t>
+          <t>0.136795314911004</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3713.934</t>
+          <t>0.140934533377299</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3706.656</t>
+          <t>0.140347450591537</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3845.061</t>
+          <t>0.141531138881089</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3934.222</t>
+          <t>0.152308223616166</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4136.295</t>
+          <t>0.136224274503082</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3804.531</t>
+          <t>0.122073733352402</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3535.481</t>
+          <t>0.116799011711007</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3430.774</t>
+          <t>0.123041720610781</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3308.836</t>
+          <t>0.11246688958183</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3291.848</t>
+          <t>0.0988859307333324</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3431.88</t>
+          <t>0.0912308842458928</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>4865.61147279986</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5260.26475498563</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5890.3219682804</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>7561.84799754381</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>9098.79701347324</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>10301.9688820546</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>11581.9492913645</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>14820.1355371551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>19051.9301776586</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>19074.1285685179</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>18853.381674901</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>20729.0518320841</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>20142.4117247399</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>22433.193698305</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>24725.2041202312</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1361.278</t>
+          <t>6241.68181664874</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1337.909</t>
+          <t>6778.39225495448</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1306.408</t>
+          <t>7479.81623255256</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1312.467</t>
+          <t>9610.98089565057</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1274.69</t>
+          <t>11499.6596404714</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1243.401</t>
+          <t>12765.8834595938</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1310.306</t>
+          <t>14253.7419407361</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1249.538</t>
+          <t>18229.4129710882</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1282.109</t>
+          <t>23545.447614308</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1378.897</t>
+          <t>23849.9414757046</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1216.608</t>
+          <t>23659.0533875489</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1143.576</t>
+          <t>26028.0190599412</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1164.707</t>
+          <t>25426.8281755285</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1202.703</t>
+          <t>28715.1500855694</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1230.186</t>
+          <t>31252.7860700043</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>197.71</t>
+          <t>45856.7321918828</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>202.97</t>
+          <t>48104.1667126075</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>209.69</t>
+          <t>52850.9585545782</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>215.37</t>
+          <t>64768.4327098009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>234.91</t>
+          <t>77277.3992290491</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>250.52</t>
+          <t>90124.2521992096</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>247.04</t>
+          <t>104004.763114836</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>279.11</t>
+          <t>130417.183581926</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>290.37</t>
+          <t>166844.501980044</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>173949.005470509</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>268.15</t>
+          <t>168766.469796782</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>283.46</t>
+          <t>193177.844510688</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>267.26</t>
+          <t>184979.705188932</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>252.91</t>
+          <t>194261.990886119</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>261.83</t>
+          <t>198266.253205199</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11.436</t>
+          <t>10539.0079969442</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>11135.2721166701</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8.712</t>
+          <t>11314.0718840078</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.797</t>
+          <t>11995.2441178959</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.484</t>
+          <t>12472.7091593847</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.732</t>
+          <t>12824.7968768763</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>13478.8913466437</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.482</t>
+          <t>14230.8714908536</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.018</t>
+          <t>15729.2879064029</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>16042.6233133076</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>3.029</t>
+          <t>16475.6934222571</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>16123.0626915325</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>16657.6405760022</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.672</t>
+          <t>18349.3052675031</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2.385</t>
+          <t>19815.8140445334</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8635.36866519866</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9066.25456029239</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>9231.73806924267</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>9711.2885869713</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>10111.8932453594</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>10508.282029058</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>11031.3959203513</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>11761.0662881777</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>12994.9003369977</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>12706.373182322</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>13129.3146385477</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>12984.7324168804</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>13440.8507255162</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>14537.5869780951</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>15659.5738999452</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5349.73076410483</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5718.63713080649</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7196.07192299571</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8860.01814882937</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10891.0542009572</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>12648.7090326278</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>14719.9125727006</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>19863.6095603866</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>22728.2712370594</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>21234.6045107225</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>19711.7568822198</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>23768.934372477</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>20804.092078363</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>19209.7777748841</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>18088.0055960303</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4052673000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4053491000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4045796000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4139088000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4269040000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4358348000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4547328000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4737114000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5004953000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4733784000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>4478890000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4385134000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>4277545000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4244452000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4451226000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5668832342.70696</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5712086837.68754</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5724446866.23941</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5810215437.61124</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5951245186.61941</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5982291723.23963</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6194354813.27753</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6404473002.73555</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6723272743.95695</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6404127963.18293</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6105093118.78332</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>5941915360.94779</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>5759768081.97418</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>5754132156.44117</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>5962960188.28848</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3749697532.25763</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3703577534.06697</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3702530545.07319</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3685673288.6053</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3713934322.3377</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3706655621.68365</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3845061211.95176</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3934221709.59554</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4136294741.06204</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3804530636.60816</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3535481208.07751</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3430774302.35543</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3308836306.52582</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3291848445.48492</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3431880034.30416</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3319350</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3309510</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3312160</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3402680</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3484980</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3564530</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3702580</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3823620</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3915630</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3859510</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>3680590</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3585490</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>3474040</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3470070</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3600340</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2396910</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2361460</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2364220</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2444140</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2508610</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2589740</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2718030</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2830980</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2901670</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2846840</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2695930</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2642340</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2576470</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2555840</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2685060</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5668832342.70696</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5712086837.68754</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5724446866.23941</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5810215437.61124</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5951245186.61941</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5982291723.23963</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6194354813.27753</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6404473002.73555</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6723272743.95695</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6404127963.18293</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6105093118.78332</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>5941915360.94779</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>5759768081.97418</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5754132156.44117</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>5962960188.28848</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4052673000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4053491000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4045796000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4139088000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4269040000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4358348000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4547328000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4737114000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5004953000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4733784000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>4478890000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4385134000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>4277545000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4244452000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4451226000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>26598.84876</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>29159.2235189638</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>33196.0416481221</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>43155.8364414454</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>55599.0483943455</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>64677.15111</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>76558.3960060623</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>100872.166821269</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>122302.795360926</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>109314.52092</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>103788.731154545</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>121405.166527261</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>113977.624023257</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>115598.518222755</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>122872.506772056</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>11591.54944</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12497.2124389638</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>14675.7091681221</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>18471.0162814454</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>22390.6500943455</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>25414.35039</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>28973.6672060623</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>38092.713971269</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>46273.6134409262</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>45084.53884</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>43370.7490745452</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>49797.0673272613</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>46230.762423257</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>47925.0499127555</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>49340.6960220562</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>87722.6441044732</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>87587.6692747521</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>90149.300591859</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>90882.2803137541</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>87610.7847952697</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>100141.045397007</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>107588.596396045</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>102577.0838589</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>112921.976546134</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>117180.506513849</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>117531.936561761</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>121345.291712594</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>125736.887699985</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>129491.790295453</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>133636.394671153</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
